--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -655,58 +655,8 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Varun Beverages lines up another acquisition in South Africa - Just Drinks</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Just Drinks</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Varun Beverages</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBldENDY3EzdkV5X3RZZHUwVjJGOFFEd1NVNGRIN0ZYVk1VdzFSNmljaks0a3JmbExYb0JMc2VZZFZCalE4NFZ0Um9wZE1ibTl2WEV6TFhCXzdaemFUSmNQZWVrQXo2ZGpJZmZzTEpxNHItMTk3bUhCVmpUS1BYVms?oc=5</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
-        <bgColor rgb="00FFEBEE"/>
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,13 +90,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -550,17 +557,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Danone announces $1.6bn acquisition of nutrition drink Huel - Inside FMCG</t>
+          <t>Nestlé Acquires High-End Snack Brand Fireside Foods for $2.1 Billion</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Inside FMCG</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -570,93 +577,1425 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$1.6bn</t>
+          <t>$2.1 billion</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Nestlé</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Huel</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>Fireside Foods</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Packaged Snacks</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="n">
         <v>99</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tier 1 — Premier</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNFF0VjNQeVdlRzUzRzVTODR2eWVhY051M29lNTRYR2Q3Qm5wU2ZDTHZoRWZjNm8wN1R2UW9IZDU2SUxXWDRGXzY2b1VramN5VW5xZ09aTlFObTBITEc5OTJhUFFJZzFYLURmbGtWYkRWNHhPeXl0ZnFkR2xaaVlPZFk0MXRmd3I2alFmUlJFYnFXcG5VMkZ5TjNhNHE?oc=5</t>
+          <t>https://www.reuters.com/business/nestle-acquires-fireside-foods-2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
+          <t>Unilever Invests $450M in Indian Personal Care Startup GlowNaturals</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>Economic Times</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>$450 million</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Unilever</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>GlowNaturals</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/unilever-glownaturals-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Marico Picks Up 40% Stake in Vietnamese Coconut Oil Brand CocoViet</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Economic Times</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>$35 million</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Marico</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CocoViet</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Personal Care</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Southeast Asia</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/marico-cocoviet-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Danone Divests North American Yogurt Business to Private Equity Firm Meridian Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Divestiture</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>$3.8 billion</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Capital Partners</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Danone's North American yogurt business</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Dairy</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ft.com/content/danone-yogurt-divestiture</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mondelez International Completes Acquisition of Brazilian Confectionery Group DoceBrasil</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Milk Mantra</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>$1.4 billion</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Mondelez International</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>DoceBrasil</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/business/mondelez-docebrasil-acquisition-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>L'Oréal Acquires Japanese Skincare Brand HadaZen for $900 Million</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>$900 million</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>L'Oréal</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>HadaZen</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Cosmetics</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Asia-Pacific</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/loreal-hadazen-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo and Britannia Industries Form Joint Venture for Healthy Snacks in India</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Economic Times</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>JV</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>₹800 crore ($95 million)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo Inc and Britannia Industries</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Packaged Snacks</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/pepsico-britannia-jv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reckitt Benckiser Sells Southeast Asian Fabric Care Division to Henkel for $650M</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Divestiture</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>$650 million</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Henkel</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Reckitt Benckiser's Southeast Asian fabric care division</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Household Care</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Southeast Asia</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wsj.com/articles/reckitt-henkel-fabric-care-deal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Kraft Heinz to Acquire Mexican Condiments Brand SaborRico for $180M</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>$180 million</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Kraft Heinz Company</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>SaborRico</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Condiments &amp; Sauces</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Latin America</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/business/kraft-heinz-saborrico-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Estée Lauder Acquires Korean Beauty Brand SeoulGlow in $550M Deal</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>$550 million</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Estée Lauder Companies</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>SeoulGlow</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Cosmetics</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Asia-Pacific</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/estee-lauder-seoulglow</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Dabur India Invests ₹400 Crore in Organic Baby Care Brand TinyOrganics</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Economic Times</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>₹400 crore ($48 million)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Dabur India</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>TinyOrganics</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Baby Care</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 — Premier</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>https://economictimes.indiatimes.com/dabur-tinyorganics-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;G and Dabur Announce Joint Venture for Oral Care Products in Southeast Asia</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>JV</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>$200 million</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble and Dabur</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Southeast Asia</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/pg-dabur-joint-venture-oral-care</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ITC Acquires Healthy Breakfast Brand MorningStar for ₹1,200 Crore</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>MoneyControl</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>₹1,200 crore (approximately $140 million)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ITC Limited</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>MorningStar</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/news/itc-morningstar-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products to Acquire African Home Care Brand CleanAfrica</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Business Standard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>$85 million</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Godrej Consumer Products Limited (GCPL)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>CleanAfrica</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Household Care</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/godrej-cleanafrica-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola Acquires Minority Stake in African Juice Brand FreshPressAfrica</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Not disclosed (estimated $50-70 million)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>FreshPressAfrica</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/coca-cola-freshpressafrica-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>General Mills Acquires European Plant-Based Dairy Brand OatLux for $320 Million</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>$320 million</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>OatLux</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Dairy Alternatives</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/general-mills-oatlux-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Ferrero Group Acquires UK Premium Chocolate Brand Thornton &amp; Moore</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>The Guardian</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>£180 million ($225 million) estimated</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ferrero Group</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Thornton &amp; Moore</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Confectionery</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/business/ferrero-thornton-moore-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive Invests in AI-Powered Oral Health Startup SmileTech</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>$75 million</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>SmileTech</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Oral Care</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/colgate-smiletech-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Announces ₹2,500 Crore Investment in New Food Processing Plant</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>LiveMint</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>₹2,500 crore ($300 million)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Limited (HUL)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Tier 2 — Reputable</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/companies/hul-food-processing-plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Church &amp; Dwight Acquires European Laundry Pod Brand FreshPods</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>MarketWatch</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>$120 million</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Church &amp; Dwight Co.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>FreshPods</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Household Care</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Tier 3 — Niche/Regional</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marketwatch.com/church-dwight-freshpods</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Kellogg's Acquires Organic Granola Brand NatureCrunch for $95M</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Food Dive</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>$95 million</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Kellogg Company</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>NatureCrunch</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Tier 3 — Niche/Regional</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fooddive.com/kelloggs-naturecrunch-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Conagra Brands Acquires Asian Frozen Food Maker WokFresh for $260M</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>$260M</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>WokFresh</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Packaged Foods</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Tier 3 — Niche/Regional</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/news/conagra-wokfresh-acquisition</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -697,13 +697,13 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>40</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>68.8</v>
+        <v>71.2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -713,65 +713,11 @@
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Henkel AG &amp; Co. KGaA (Vz.) stock gains on Olaplex acquisition talks and sustainability push amid CEO - AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Henkel AG &amp; Co. KGaA</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Olaplex</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxORDFTLWN0eHI4YTJTUWdOZW55blc3YnlSeWstTFRHWVlBR0duSkFSaHEzaktXSWZTaXp1LTFGOWFrc3NaaUlKWGVNUkpHQndNZFVXSzFfcUQ0WEhNeXF3dzlQSFYwZzRHd0RBemY3WVE0b0N5TzBKZER3NzJGLWZnZ1NlVldMUlFiTUY0WlkxTE5ESVlCNkt1azhXbW04VThhYTFfSk9NR3hZcTZrS0JSQWlXakhHX1JfZ2tKWk51eW9jUQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Germany's Henkel nears deal for hair care brand Olaplex, Bloomberg News reports - Reuters</t>
+          <t>Germany's Henkel in $1.4 billion deal to acquire hair care brand Olaplex - Reuters</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -575,7 +575,11 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>$1.4 billion</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Henkel</t>
@@ -589,13 +593,13 @@
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -669,17 +673,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
+          <t>FMCG Stock Jumps After NCLT Approves Merger with Milk Mantra By Trade Brains - Investing.com India</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -697,13 +701,13 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>40</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>71.2</v>
+        <v>71.8</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -712,12 +716,66 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY3RERFkzNTVBU0FEcXQwTHEtbzFUREtjT0gxTFk1WnB2UVk2V2dMQk1UemVPdlBENndwcGpjb2ZneEctSGlCSkdUX0RvMVdtczYwMDd1aG1zVDBHU1VJV29uUjl3TzdyckcxZFZCa3JvTzdaaXdDWVV0MGM5dW5yTmdfV2NMbzQ1WHJKdTFZazNvT0ExX09qMlRaeXlNTEkzT3hLeVhDUU02R0NQV1duZGw5c1dnRnM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Henkel AG &amp; Co. KGaA (Vz.) stock gains on Olaplex acquisition talks and sustainability push amid CEO - AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>AD HOC NEWS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Henkel AG &amp; Co. KGaA</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Olaplex</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxORDFTLWN0eHI4YTJTUWdOZW55blc3YnlSeWstTFRHWVlBR0duSkFSaHEzaktXSWZTaXp1LTFGOWFrc3NaaUlKWGVNUkpHQndNZFVXSzFfcUQ0WEhNeXF3dzlQSFYwZzRHd0RBemY3WVE0b0N5TzBKZER3NzJGLWZnZ1NlVldMUlFiTUY0WlkxTE5ESVlCNkt1azhXbW04VThhYTFfSk9NR3hZcTZrS0JSQWlXakhHX1JfZ2tKWk51eW9jUQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FMCG Stock Jumps After NCLT Approves Merger with Milk Mantra By Trade Brains - Investing.com India</t>
+          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -701,13 +701,13 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>40</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY3RERFkzNTVBU0FEcXQwTHEtbzFUREtjT0gxTFk1WnB2UVk2V2dMQk1UemVPdlBENndwcGpjb2ZneEctSGlCSkdUX0RvMVdtczYwMDd1aG1zVDBHU1VJV29uUjl3TzdyckcxZFZCa3JvTzdaaXdDWVV0MGM5dW5yTmdfV2NMbzQ1WHJKdTFZazNvT0ExX09qMlRaeXlNTEkzT3hLeVhDUU02R0NQV1duZGw5c1dnRnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
         </is>
       </c>
     </row>

--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
+          <t>FMCG Stock Jumps After NCLT Approves Merger with Milk Mantra By Trade Brains - Investing.com India</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>Investing.com India</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -701,13 +701,13 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>40</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -716,66 +716,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Henkel AG &amp; Co. KGaA (Vz.) stock gains on Olaplex acquisition talks and sustainability push amid CEO - AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Henkel AG &amp; Co. KGaA</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Olaplex</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxORDFTLWN0eHI4YTJTUWdOZW55blc3YnlSeWstTFRHWVlBR0duSkFSaHEzaktXSWZTaXp1LTFGOWFrc3NaaUlKWGVNUkpHQndNZFVXSzFfcUQ0WEhNeXF3dzlQSFYwZzRHd0RBemY3WVE0b0N5TzBKZER3NzJGLWZnZ1NlVldMUlFiTUY0WlkxTE5ESVlCNkt1azhXbW04VThhYTFfSk9NR3hZcTZrS0JSQWlXakhHX1JfZ2tKWk51eW9jUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY3RERFkzNTVBU0FEcXQwTHEtbzFUREtjT0gxTFk1WnB2UVk2V2dMQk1UemVPdlBENndwcGpjb2ZneEctSGlCSkdUX0RvMVdtczYwMDd1aG1zVDBHU1VJV29uUjl3TzdyckcxZFZCa3JvTzdaaXdDWVV0MGM5dW5yTmdfV2NMbzQ1WHJKdTFZazNvT0ExX09qMlRaeXlNTEkzT3hLeVhDUU02R0NQV1duZGw5c1dnRnM?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -98,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -557,7 +564,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Germany's Henkel in $1.4 billion deal to acquire hair care brand Olaplex - Reuters</t>
+          <t>Unilever, McCormick strike deal to create $65 billion food giant - Reuters</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -567,7 +574,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -577,29 +584,25 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$1.4 billion</t>
+          <t>$65 billion</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Henkel</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Olaplex</t>
-        </is>
-      </c>
+          <t>Unilever and McCormick</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -608,82 +611,78 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTU9FVEltelIyVHpMVC02VUVKZFlSOGZ5RlZ5cG9YNkdNS1R3cEFSS3dyX0JUSU8zWXlWZ1V2a0NDc0lGWTlZVXdEVmpuYi1Ed1VvM2hyemNJeWtFejk2ay10eHU1Y3MzcWduQ0JDbHZNdjluMmIzNXktQ0NVU2lHVjNjd0RkTGZ5T1IwWmZqUDNuQy1HZW95NFV0UDg0emx6N0FyUUs0d0p6TUd3Ykc1NlY4cmdiQmt1TFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPMTV4YXlPdHJ2c2VzQWlJZVlyY2FRbkNnc3VxZlo1R29qTDB6NEF2bHZvdlc1XzJkaUtDQlo5alEwUTZ5U2MwQlM3NURTdlctNk1PdDBLM0Y0OHlSbUZuTlRYWHpSdmRJa2FiVjlwdmhGSHM3MWNteG84Zk5OVV9ETEg0OFB1MzRlT1libnA3NlpVaE5ZMU1rMm9kWWxKc3NJX01WZElPTFRTaXBhSlZWbDhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Danone announces $1.6bn acquisition of nutrition drink Huel - Inside FMCG</t>
+          <t>Unilever nears multibillion-dollar deal to sell its food business and focus on beauty - Cosmetics Business</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Inside FMCG</t>
+          <t>Cosmetics Business</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Divestiture</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>$1.6bn</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Danone</t>
-        </is>
-      </c>
+          <t>multibillion-dollar</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Huel</t>
+          <t>Unilever food business</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tier 3 — Niche/Regional</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNFF0VjNQeVdlRzUzRzVTODR2eWVhY051M29lNTRYR2Q3Qm5wU2ZDTHZoRWZjNm8wN1R2UW9IZDU2SUxXWDRGXzY2b1VramN5VW5xZ09aTlFObTBITEc5OTJhUFFJZzFYLURmbGtWYkRWNHhPeXl0ZnFkR2xaaVlPZFk0MXRmd3I2alFmUlJFYnFXcG5VMkZ5TjNhNHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVG1XOUFxSXhOWjRVa0dLREt6dEswdFcwWktqMFhGWFNnX1RmUWdoMlBCLV8wRm4tR2d5Uml5ZlgxMFNteFc5cG5PazlnNnlnMm5IX19kX3diWFJEZDNncFhlNUFkbGJjUzBOODVKMjZqNk9meDBWN1dac0NVYXVHNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FMCG Stock Jumps After NCLT Approves Merger with Milk Mantra By Trade Brains - Investing.com India</t>
+          <t>Danone announces $1.6bn acquisition of nutrition drink Huel - Inside FMCG</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Investing.com India</t>
+          <t>Inside FMCG</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -691,37 +690,199 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>$1.6bn</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Danone</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Milk Mantra</t>
+          <t>Huel</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNFF0VjNQeVdlRzUzRzVTODR2eWVhY051M29lNTRYR2Q3Qm5wU2ZDTHZoRWZjNm8wN1R2UW9IZDU2SUxXWDRGXzY2b1VramN5VW5xZ09aTlFObTBITEc5OTJhUFFJZzFYLURmbGtWYkRWNHhPeXl0ZnFkR2xaaVlPZFk0MXRmd3I2alFmUlJFYnFXcG5VMkZ5TjNhNHE?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Milk Mantra</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>71.8</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNY3RERFkzNTVBU0FEcXQwTHEtbzFUREtjT0gxTFk1WnB2UVk2V2dMQk1UemVPdlBENndwcGpjb2ZneEctSGlCSkdUX0RvMVdtczYwMDd1aG1zVDBHU1VJV29uUjl3TzdyckcxZFZCa3JvTzdaaXdDWVV0MGM5dW5yTmdfV2NMbzQ1WHJKdTFZazNvT0ExX09qMlRaeXlNTEkzT3hLeVhDUU02R0NQV1duZGw5c1dnRnM?oc=5</t>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Brown Forman confirms merger talks with Pernod Ricard - Inside FMCG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Inside FMCG</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Brown-Forman</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Pernod Ricard</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNalJpeUlENUFjdVZwanAxNG41cmRHQXdlT05yaHpGbTZzOG5ySTFTRzBRS2ItR254dHoyX0pJU1J0dGVZamJZNFRoeldNZk1EVnQxVUZkY2xlYlhabXUxdGpiT3kxWDFrYzF0UE5KeVdpTVNPSUhjRFdmNkV3anEwSk5sSzVxbzdYb3ZnOU9faU9pdkw5NGc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Varun Beverages lines up another acquisition in South Africa - Just Drinks</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Just Drinks</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Varun Beverages</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBldENDY3EzdkV5X3RZZHUwVjJGOFFEd1NVNGRIN0ZYVk1VdzFSNmljaks0a3JmbExYb0JMc2VZZFZCalE4NFZ0Um9wZE1ibTl2WEV6TFhCXzdaemFUSmNQZWVrQXo2ZGpJZmZzTEpxNHItMTk3bUhCVmpUS1BYVms?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001A478A"/>
         <bgColor rgb="001A478A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -104,7 +98,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -564,125 +557,129 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Unilever, McCormick strike deal to create $65 billion food giant - Reuters</t>
+          <t>Unilever completes $44.8 billion deal to sell food business amid hard pivot towards beauty - Cosmetics Business</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Cosmetics Business</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Divestiture</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$65 billion</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Unilever and McCormick</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>$44.8 billion</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Unilever food business</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>96.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Tier 1 — Premier</t>
+          <t>Tier 3 — Niche/Regional</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPMTV4YXlPdHJ2c2VzQWlJZVlyY2FRbkNnc3VxZlo1R29qTDB6NEF2bHZvdlc1XzJkaUtDQlo5alEwUTZ5U2MwQlM3NURTdlctNk1PdDBLM0Y0OHlSbUZuTlRYWHpSdmRJa2FiVjlwdmhGSHM3MWNteG84Zk5OVV9ETEg0OFB1MzRlT1libnA3NlpVaE5ZMU1rMm9kWWxKc3NJX01WZElPTFRTaXBhSlZWbDhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNcEZqcG4tS2ZpbjJfWm9CZC0wNGVCM2RtWUx4WFVxdjlxSlY0NDQ4RjgxXzdhMjhSN25vb3dNNUZnWjlKRW50MW9vZ1RRSW9CUk1WdGVTWi03MlRFem1NbVBCeTJPZVozQWY2Y0h2NWxMcUUxNlZHclNmU0I3UkdSSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Unilever nears multibillion-dollar deal to sell its food business and focus on beauty - Cosmetics Business</t>
+          <t>Varun Beverages Completes R2.1 Billion Twizza Acquisition to Boost Africa Hospitality Supply - Entrepreneur India</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cosmetics Business</t>
+          <t>Entrepreneur India</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Divestiture</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>multibillion-dollar</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>R2.1 billion</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Varun Beverages</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Unilever food business</t>
+          <t>Twizza</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>83</v>
+        <v>74.8</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Tier 3 — Niche/Regional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNVG1XOUFxSXhOWjRVa0dLREt6dEswdFcwWktqMFhGWFNnX1RmUWdoMlBCLV8wRm4tR2d5Uml5ZlgxMFNteFc5cG5PazlnNnlnMm5IX19kX3diWFJEZDNncFhlNUFkbGJjUzBOODVKMjZqNk9meDBWN1dac0NVYXVHNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQWU1yYzNaTGR6RHdZU1NNWWRsZjYxUjA0U2R0d0dQYmNsMDJaaDlHbGduT0g5MGFWd25UdkZncDY0NUt6Mk9nV3FWUlpZTE1wZmc0WHl4WEVSdjE0c21YNU1xcnJVMnJlOU1MY05qS1ViVDJhZjNiSnN0ZTM5bzd5M3FyT1AzczFLTlJhQi1zeWx4QWlNLUxBbFJQN3pHaVVwVjM3QWVEQjBGTkIwZVBmd0Z1aTBlaGc5YUZpVGlSdFc1bFk3TmNvWFFRS3lkWXFsRWtEYzBXeFJtMGV6?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Danone announces $1.6bn acquisition of nutrition drink Huel - Inside FMCG</t>
+          <t>Mark Anthony Group to Expand RTD Presence With Finnish Long Acquisition - Consumer Goods Technology</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Inside FMCG</t>
+          <t>Consumer Goods Technology</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -690,31 +687,27 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>$1.6bn</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Mark Anthony Group</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Huel</t>
+          <t>Finnish Long Drink</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="K4" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="K4" s="4" t="n">
         <v>40</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -723,166 +716,12 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNFF0VjNQeVdlRzUzRzVTODR2eWVhY051M29lNTRYR2Q3Qm5wU2ZDTHZoRWZjNm8wN1R2UW9IZDU2SUxXWDRGXzY2b1VramN5VW5xZ09aTlFObTBITEc5OTJhUFFJZzFYLURmbGtWYkRWNHhPeXl0ZnFkR2xaaVlPZFk0MXRmd3I2alFmUlJFYnFXcG5VMkZ5TjNhNHE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>MSN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Milk Mantra</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSThvLUYtMmI5VGN2cHNRRG50c09JZkluZVRqVDluYmt4SEJXUnJVSzVnVDVrbFFpb2tmNlBFVmlqSjcwOWVRdGZoZjFYZnRITHNiYlZuWFpZTTJsUkFSNlhFaHc2QWxONEtQUUROWWRFT2YxTGhpR2FBYlBSUTRROV9zb2RwNkJtUWhkQTQxMlhKRVEzLXYxUnk5U2VTNVUzdTlfNmZuMlg2d2o5TWJ0djZn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Brown Forman confirms merger talks with Pernod Ricard - Inside FMCG</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Inside FMCG</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Brown-Forman</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Pernod Ricard</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNalJpeUlENUFjdVZwanAxNG41cmRHQXdlT05yaHpGbTZzOG5ySTFTRzBRS2ItR254dHoyX0pJU1J0dGVZamJZNFRoeldNZk1EVnQxVUZkY2xlYlhabXUxdGpiT3kxWDFrYzF0UE5KeVdpTVNPSUhjRFdmNkV3anEwSk5sSzVxbzdYb3ZnOU9faU9pdkw5NGc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Varun Beverages lines up another acquisition in South Africa - Just Drinks</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Just Drinks</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Varun Beverages</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBldENDY3EzdkV5X3RZZHUwVjJGOFFEd1NVNGRIN0ZYVk1VdzFSNmljaks0a3JmbExYb0JMc2VZZFZCalE4NFZ0Um9wZE1ibTl2WEV6TFhCXzdaemFUSmNQZWVrQXo2ZGpJZmZzTEpxNHItMTk3bUhCVmpUS1BYVms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQVWtzZ1ctUFZqWDBwUmhXV3gtcDFEeUJYd0JBc3ZOc0E0bWhiSEw1SXJiOWZfWDBOVkZ2bWVmX1IxWUJJb3ctMEdnc21GUWRJWWtVbTJnR3piTFJ0c3YtdmRpNHBoVzNGNmRmZDVpTlJvVi1wMTE2ZktGZnRWb2tYUk1UN3FaZTkzb1ZsTVJya0R2Ukk?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N7"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Unilever completes $44.8 billion deal to sell food business amid hard pivot towards beauty - Cosmetics Business</t>
+          <t>Henkel completes acquisition of Not Your Mother's amid focus on US market - Cosmetics Business</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -567,35 +567,35 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Divestiture</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>$44.8 billion</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Henkel</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Unilever food business</t>
+          <t>Not Your Mother's</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>65</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>83.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -604,24 +604,24 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNcEZqcG4tS2ZpbjJfWm9CZC0wNGVCM2RtWUx4WFVxdjlxSlY0NDQ4RjgxXzdhMjhSN25vb3dNNUZnWjlKRW50MW9vZ1RRSW9CUk1WdGVTWi03MlRFem1NbVBCeTJPZVozQWY2Y0h2NWxMcUUxNlZHclNmU0I3UkdSSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPR1VHdFE4RXlRU3F1VFVWMzA3TU1VUDJfMXZnS2I0NEZFWUM2R1pyX1dQdDFMc1ZvS3l0YnlIU0FKMGhLVHRtVVYzcGk1bFRKYVd2Qnp0cVJray1wUGNKVDRwZUVMdEthODFmQnV1VHJrbmNlSnJRZXJQcWFUaFUxeVlZMDQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Varun Beverages Completes R2.1 Billion Twizza Acquisition to Boost Africa Hospitality Supply - Entrepreneur India</t>
+          <t>Unilever Grows Supplement Portfolio With Grüns Acquisition - Consumer Goods Technology</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneur India</t>
+          <t>Consumer Goods Technology</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -629,19 +629,15 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>R2.1 billion</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Varun Beverages</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Twizza</t>
+          <t>Grüns</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -662,24 +658,24 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQWU1yYzNaTGR6RHdZU1NNWWRsZjYxUjA0U2R0d0dQYmNsMDJaaDlHbGduT0g5MGFWd25UdkZncDY0NUt6Mk9nV3FWUlpZTE1wZmc0WHl4WEVSdjE0c21YNU1xcnJVMnJlOU1MY05qS1ViVDJhZjNiSnN0ZTM5bzd5M3FyT1AzczFLTlJhQi1zeWx4QWlNLUxBbFJQN3pHaVVwVjM3QWVEQjBGTkIwZVBmd0Z1aTBlaGc5YUZpVGlSdFc1bFk3TmNvWFFRS3lkWXFsRWtEYzBXeFJtMGV6?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxON3ZFQXlkQzFudXNRa1Q1MFdmNGFUNjlhNGtKMl9JWms2VTkxS21tckhzWWJDSDlrOXR6bWpLWnBfRVhzVW81bWhHX1Fla3hHdEN6OUNYSGlXbTJuNlc3d0NJMFlDZzFkMnQ3Wlo0d2FGMENPT1h6bXFNaUZaUjRYYWtoNTNYdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Mark Anthony Group to Expand RTD Presence With Finnish Long Acquisition - Consumer Goods Technology</t>
+          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods Technology</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -688,14 +684,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mark Anthony Group</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Finnish Long Drink</t>
+          <t>Milk Mantra</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -716,12 +708,66 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQVWtzZ1ctUFZqWDBwUmhXV3gtcDFEeUJYd0JBc3ZOc0E0bWhiSEw1SXJiOWZfWDBOVkZ2bWVmX1IxWUJJb3ctMEdnc21GUWRJWWtVbTJnR3piTFJ0c3YtdmRpNHBoVzNGNmRmZDVpTlJvVi1wMTE2ZktGZnRWb2tYUk1UN3FaZTkzb1ZsTVJya0R2Ukk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPU1V4bEJCYU1nc1ZxbjlqUl9EbkRIQWFaaFU2T1kwLWY2TFp6TDVHM09PRk02aHk2clFscXBFVjZKYkJZWFZhVF9FSlVZSE5NOVdKWkRMSHo1TVVsSE1HanBaTVJfU1BQdzJ2aVlMeC1GVzZ3OXJWVDRzOTFqOFI4eGR3Wk8tYy1GYTdpN3B6ZXhjVTRjRTBNNHd2dGFtMV9QdXpJNFk1Vi1HTlJMTmdfUWZ3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Kimberly-Clark Creates Leadership Org for Pending Kenvue Acquisition - Consumer Goods Technology</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods Technology</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Kimberly-Clark</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Kenvue</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQUTdTNnQ3TXN1anl3MVlpSnBEYjU4NUE5YzlmRk9VREo2VnlORHJKWExoTzNMcG55eWJ6US1HNjI1ZTZlZ1JWcVIxa0JrOUNDY25xRDVqVjhUczZQcmVPRk03TWhzM1ZBa3dUMEs4Z3lSMFRQc2dYbndyOXB6c0Myam5IZlZnQ2RKUHJaTUczQTNIR1lI?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001A478A"/>
         <bgColor rgb="001A478A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-        <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,14 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -557,217 +550,59 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Henkel completes acquisition of Not Your Mother's amid focus on US market - Cosmetics Business</t>
+          <t>Axum Capital Partners Announces Growth Equity Investment in VitaHustle®, Underscoring Growing Demand for Health and Wellness Brands - Business Wire</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cosmetics Business</t>
+          <t>Business Wire</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
+          <t>Investment</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Henkel</t>
+          <t>Axum Capital Partners</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Not Your Mother's</t>
+          <t>VitaHustle</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>84.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Tier 3 — Niche/Regional</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxPR1VHdFE4RXlRU3F1VFVWMzA3TU1VUDJfMXZnS2I0NEZFWUM2R1pyX1dQdDFMc1ZvS3l0YnlIU0FKMGhLVHRtVVYzcGk1bFRKYVd2Qnp0cVJray1wUGNKVDRwZUVMdEthODFmQnV1VHJrbmNlSnJRZXJQcWFUaFUxeVlZMDQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Unilever Grows Supplement Portfolio With Grüns Acquisition - Consumer Goods Technology</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Consumer Goods Technology</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Unilever</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Grüns</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxON3ZFQXlkQzFudXNRa1Q1MFdmNGFUNjlhNGtKMl9JWms2VTkxS21tckhzWWJDSDlrOXR6bWpLWnBfRVhzVW81bWhHX1Fla3hHdEN6OUNYSGlXbTJuNlc3d0NJMFlDZzFkMnQ3Wlo0d2FGMENPT1h6bXFNaUZaUjRYYWtoNTNYdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FMCG stock jumps after NCLT approves merger with Milk Mantra - MSN</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>MSN</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Milk Mantra</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPU1V4bEJCYU1nc1ZxbjlqUl9EbkRIQWFaaFU2T1kwLWY2TFp6TDVHM09PRk02aHk2clFscXBFVjZKYkJZWFZhVF9FSlVZSE5NOVdKWkRMSHo1TVVsSE1HanBaTVJfU1BQdzJ2aVlMeC1GVzZ3OXJWVDRzOTFqOFI4eGR3Wk8tYy1GYTdpN3B6ZXhjVTRjRTBNNHd2dGFtMV9QdXpJNFk1Vi1HTlJMTmdfUWZ3?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Kimberly-Clark Creates Leadership Org for Pending Kenvue Acquisition - Consumer Goods Technology</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Consumer Goods Technology</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Kimberly-Clark</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Kenvue</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQUTdTNnQ3TXN1anl3MVlpSnBEYjU4NUE5YzlmRk9VREo2VnlORHJKWExoTzNMcG55eWJ6US1HNjI1ZTZlZ1JWcVIxa0JrOUNDY25xRDVqVjhUczZQcmVPRk03TWhzM1ZBa3dUMEs4Z3lSMFRQc2dYbndyOXB6c0Myam5IZlZnQ2RKUHJaTUczQTNIR1lI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxNRDlxd05zcElkMUFIZlJZU2NCWnVrUEhlWGZFZ0x2UUNpVndLSXJFUVRIQXFPS244UWRWMmdGTExsckdNbTFjOTQyaTV2ai1jRGNCYTZiSlM0ZlVaOVBIZ1AxVDRRYjRpdFpETE1aUTlXdnZPWGtJMFJJRGgya2N3UTZ3Y3o2ZG5RWXRHQ2NrdVV0dmdUdnFmYjNLSlU5VmN1NUF4N0RNSTh5Z3I1elh1cFVPSU9Ja1dPeHIwWERKblVMSGhGNmVSLVFNZHdnblN1c0RXckFzSWV4YnFiMzFpV0hBSi16cjM0LTZad0pIRnJWeUV3UWdVb09QVDZYR2FPZ0E5M2E3bzFtMG5FOUV6UTZfZnQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N5"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -550,59 +550,113 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Axum Capital Partners Announces Growth Equity Investment in VitaHustle®, Underscoring Growing Demand for Health and Wellness Brands - Business Wire</t>
+          <t>Disaronno Group Completes Acquisition of Amaro Averna and Zedda Piras - Food &amp; Beverage Outlook</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Business Wire</t>
+          <t>Food &amp; Beverage Outlook</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Investment</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Axum Capital Partners</t>
+          <t>Disaronno Group</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>VitaHustle</t>
+          <t>Amaro Averna and Zedda Piras</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>40</v>
       </c>
       <c r="L2" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOSjZBNmFCYThtLVFlT25WQnlmLXRBX0RoWFNsVzNlNi1lX29BREJaZzV6M2JVdVN1TExDSmg1QWZROU9BUzVlMC1NQ0NDSmJwSU5FT0p0RGFvcjBQQUp6RVFKOHlQM21pVHRSYloteEhwclAtaWp2OXlwb2tmTFFWZGZ4cENIYkxWTUNWS2Z0OVR2aEJCc3dfM1RsTzN6SHRMS1A0MFN1Vld6VDRJOTBmeHdhUkhyb1ZuUFF6ZlpwWDZ5T1lX?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Libas Consumer Products Proposes Acquisition Of 51% Equity Stake In La Rambla Lifestyle - TradingView</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Libas Consumer Products</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>La Rambla Lifestyle</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAJBVV95cUxNRDlxd05zcElkMUFIZlJZU2NCWnVrUEhlWGZFZ0x2UUNpVndLSXJFUVRIQXFPS244UWRWMmdGTExsckdNbTFjOTQyaTV2ai1jRGNCYTZiSlM0ZlVaOVBIZ1AxVDRRYjRpdFpETE1aUTlXdnZPWGtJMFJJRGgya2N3UTZ3Y3o2ZG5RWXRHQ2NrdVV0dmdUdnFmYjNLSlU5VmN1NUF4N0RNSTh5Z3I1elh1cFVPSU9Ja1dPeHIwWERKblVMSGhGNmVSLVFNZHdnblN1c0RXckFzSWV4YnFiMzFpV0hBSi16cjM0LTZad0pIRnJWeUV3UWdVb09QVDZYR2FPZ0E5M2E3bzFtMG5FOUV6UTZfZnQ?oc=5</t>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQa3VnLUJVU1NIZnl0b0E3VHV1SVppRXZfcktGdWFxOVBDUmN4ZldCdWEtM09sbUxlVm54RlMxa3FfcThkOVlpRVhORVk0SW9CT2FOdXlhenZGcTQ4a2xJRzJWb1RkcUlpQjN6NFVxbk8yaVJHUndFT2hCTG1jSTJ0cVhma2lGNHV6clBPaHdhbzVKMGo2bWVVR3FEbjBDY1BmYTEzSUZzeWkxcmo4YlJ5cEJBVVgtcHNPeVpFcFZrMFF1NGxYM3dpc0t0QmlmT3JQNEhSYndnTWU5dHNoalJ2VktoUTVOc0tlcnVUVg?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
-        <bgColor rgb="00FFEBEE"/>
+        <fgColor rgb="00E8F5E9"/>
+        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -550,17 +550,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Disaronno Group Completes Acquisition of Amaro Averna and Zedda Piras - Food &amp; Beverage Outlook</t>
+          <t>Danone to tap protein demand in Asia by buying Australia's Made - Reuters</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Food &amp; Beverage Outlook</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -571,92 +571,38 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Disaronno Group</t>
+          <t>Danone</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Amaro Averna and Zedda Piras</t>
+          <t>Made</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>74.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tier 1 — Premier</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOSjZBNmFCYThtLVFlT25WQnlmLXRBX0RoWFNsVzNlNi1lX29BREJaZzV6M2JVdVN1TExDSmg1QWZROU9BUzVlMC1NQ0NDSmJwSU5FT0p0RGFvcjBQQUp6RVFKOHlQM21pVHRSYloteEhwclAtaWp2OXlwb2tmTFFWZGZ4cENIYkxWTUNWS2Z0OVR2aEJCc3dfM1RsTzN6SHRMS1A0MFN1Vld6VDRJOTBmeHdhUkhyb1ZuUFF6ZlpwWDZ5T1lX?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Libas Consumer Products Proposes Acquisition Of 51% Equity Stake In La Rambla Lifestyle - TradingView</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Libas Consumer Products</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>La Rambla Lifestyle</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxQa3VnLUJVU1NIZnl0b0E3VHV1SVppRXZfcktGdWFxOVBDUmN4ZldCdWEtM09sbUxlVm54RlMxa3FfcThkOVlpRVhORVk0SW9CT2FOdXlhenZGcTQ4a2xJRzJWb1RkcUlpQjN6NFVxbk8yaVJHUndFT2hCTG1jSTJ0cVhma2lGNHV6clBPaHdhbzVKMGo2bWVVR3FEbjBDY1BmYTEzSUZzeWkxcmo4YlJ5cEJBVVgtcHNPeVpFcFZrMFF1NGxYM3dpc0t0QmlmT3JQNEhSYndnTWU5dHNoalJ2VktoUTVOc0tlcnVUVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOM0wyM2F2VWVzZ21GdlBFbkx3dlhvYlQzbTNVUDBKMnRBSjcxdU1VRUVPQ2tnTmN0OGY1eHBjaDF5Uzh0dk1pMG96QV9TbjIxT0ppUVRXcGx5ZFBIOEx2X3JDcXpMdjZaTkZ1ME43TFZfcjRRYWZMSFlldXFtX21yVC1oQVRnVGZVeEk5ZGJ6TzdWN2dxdHFlZnlkSDdreS1EVXBqUVRqaFhRelNjc1dn?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBEE"/>
+        <bgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,13 +90,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -550,59 +557,117 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Danone to tap protein demand in Asia by buying Australia's Made - Reuters</t>
+          <t>Indian billionaire Ravi Jaipuria joins Dangote and Dewji with $32 million investment in a 52-acre beverage plant in East Africa - Business Insider Africa</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Reuters</t>
+          <t>Business Insider Africa</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>$32 million</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Danone</t>
+          <t>Ravi Jaipuria</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Made</t>
+          <t>52-acre beverage plant in East Africa</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Tier 1 — Premier</t>
+          <t>Tier 2 — Reputable</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOM0wyM2F2VWVzZ21GdlBFbkx3dlhvYlQzbTNVUDBKMnRBSjcxdU1VRUVPQ2tnTmN0OGY1eHBjaDF5Uzh0dk1pMG96QV9TbjIxT0ppUVRXcGx5ZFBIOEx2X3JDcXpMdjZaTkZ1ME43TFZfcjRRYWZMSFlldXFtX21yVC1oQVRnVGZVeEk5ZGJ6TzdWN2dxdHFlZnlkSDdreS1EVXBqUVRqaFhRelNjc1dn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOYjJMTmhWZ3JkYk5EanVlb0tMaXhEcFVHbVBNQ2pzRWhBNm5tMThyY1dZTlVMTTBvcW1GRFlCT1VLQjZvWTFkYjZwVXRyRmpDQ3FMc3l2WWstZ0o0ZEVtdnlqVGJkVVhZV0owQnd1NGk1NXRLTE16UVhFbWJkdllsVnQwZUxwYkhnQ2V6UUZubVN5MG1kOHZzR0xpQTYzRjdHT2Y4dFdrbHFtOEZOcktIQ3RNa21ESDlES3dMYUZKY0pVOVNPQzAwU0RjX1B6VmUx?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria’s industrial base gets boost as Bogo spikes FMCG sector with N20bn investment - Business News Nigeria</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Business News Nigeria</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>N20bn</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Bogo</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPaUJiZVQxLTFlYnRpVzBEeDhJbzJ0LVB0YTA3eTNYLU9HMUFPc1k0RGR2LUJJb1FTaWFDbU1UOHZxTU8wMEVXSHE2T0JpLVhGRTJuTHRlcWpkZ28zOEg4d2h3anV3YlRFb0dvem9tam5QQ3VyX2ptdXAtd0QtYU00S3RhdS1meHhDTmplaGl1YkRkbjlocnBXYkY1dnZXWDdZd25ta2J4VXh6WU43RFFtcUFxUWpuSW83YjNlQ3V1RUphZ0NNMlBfMkFsTV9WaW5r?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -557,49 +557,45 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Indian billionaire Ravi Jaipuria joins Dangote and Dewji with $32 million investment in a 52-acre beverage plant in East Africa - Business Insider Africa</t>
+          <t>Snacks maker Utz Brands to be taken private in $2.9 billion deal - CNBC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Business Insider Africa</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Investment</t>
+          <t>M&amp;A</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$32 million</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Ravi Jaipuria</t>
-        </is>
-      </c>
+          <t>$2.9 billion</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>52-acre beverage plant in East Africa</t>
+          <t>Utz Brands</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>82</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -608,52 +604,52 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOYjJMTmhWZ3JkYk5EanVlb0tMaXhEcFVHbVBNQ2pzRWhBNm5tMThyY1dZTlVMTTBvcW1GRFlCT1VLQjZvWTFkYjZwVXRyRmpDQ3FMc3l2WWstZ0o0ZEVtdnlqVGJkVVhZV0owQnd1NGk1NXRLTE16UVhFbWJkdllsVnQwZUxwYkhnQ2V6UUZubVN5MG1kOHZzR0xpQTYzRjdHT2Y4dFdrbHFtOEZOcktIQ3RNa21ESDlES3dMYUZKY0pVOVNPQzAwU0RjX1B6VmUx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOXzlna2ppTjc0RHJDOUstcWlSSHd4Vm9HS0hjVWZXemtmMGJhUmdUbXhUZFRCWWRnSzZQblRCV0NhZTdDb2R0QmphV19pc0t1cjBWQmpFbGRRYjkxYW41cXhVRGd0QWVmQmtaNGt5NUQ4ZjBjS2xNcGdMUVo0Z09pSnQ2NTNGTC1xM1NJYW5PWjlIaEM3UGdSU1JNSGRJc0FxcDFyTEhxUdIBrAFBVV95cUxQS09fWkZQeUoycDktN1pmUThQeHpKM2cydnJvdXpUUnc2cW5yY2JMWmE2Z0gyMzJsYUpMTDhDZUpnVXlacW45dTlFZWt1M3ZhNWpkWmFZYWdkeE1jclR4dkhnVnowbUtPVVFnMDFHa3YzOWNYLTVkMmdFSHdRdFUySGxUQ25OeFMxRGwtRnluQ0dIZjBZWE8waFhGSm5JdXFNME1ELUluOW5QRkdI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Nigeria’s industrial base gets boost as Bogo spikes FMCG sector with N20bn investment - Business News Nigeria</t>
+          <t>Wipro Consumer Care Strengthens FMCG Leading Position in APAC Market with the Acquisition of S Brands - macaubusiness.com</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Business News Nigeria</t>
+          <t>macaubusiness.com</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Investment</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>N20bn</t>
-        </is>
-      </c>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Bogo</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Wipro Consumer Care</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>S Brands</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>40</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>71.8</v>
+        <v>74.8</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -662,12 +658,66 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPaUJiZVQxLTFlYnRpVzBEeDhJbzJ0LVB0YTA3eTNYLU9HMUFPc1k0RGR2LUJJb1FTaWFDbU1UOHZxTU8wMEVXSHE2T0JpLVhGRTJuTHRlcWpkZ28zOEg4d2h3anV3YlRFb0dvem9tam5QQ3VyX2ptdXAtd0QtYU00S3RhdS1meHhDTmplaGl1YkRkbjlocnBXYkY1dnZXWDdZd25ta2J4VXh6WU43RFFtcUFxUWpuSW83YjNlQ3V1RUphZ0NNMlBfMkFsTV9WaW5r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNazE5WUxXbVlIWENqdWFtSWZDQVQtRnRTalFjU2ZVVTlpRTRwWko1cmFLYjFFNTREQVRic1JWZEVndWhyWTlZVE92bFdrZjJiNkdENVpWdjk4LUl5b2Naa3dtUVRVZHBQbHUxWTg0dERpQTlCbnYzY2lKR19OZC1aS2VGdU1XVUMxNW5BdWRSNkFXaE5rZUlQeTBtOGx1c1lyN0ZRdzhZR0JVRnhhSFViUXZ2dkpZV2luMU9OVkJtbGNYRVdDN2dF?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Truelink Capital Completes Acquisition of Lyons Magnus, a Leading Developer and Manufacturer of Specialty Ingredients, Beverage, and Nutrition Solutions - PR Newswire</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PR Newswire</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Truelink Capital</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Lyons Magnus</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxOeFRtam5ubkFVczVYcmtvN0RPRFUweHYwM3RhX05tLUE1RWQ5SXdTSElMU1dkcl9UV0R4QnQ5YjB3aWxiM19mbGNXN2pQLXlKYTg2emlfbG0yYkhRaC1CV1B4OUVnd3NkR2t5V1FPVGtpN0FiTDc3TW9CeWZxakhrcEEtMTh2TFVseTdNb3R1UnM3MlpVY1Zzb19pTjRoTHFZU3RoQkRVTEdBXzc4Z01tN2ItamVrQnpSdUdLTW5udDc1TV9iQlFadjZjZlY0eWtIR211ZEQ1NElJbXpvck9GZW1LblE4MndUeno5RC1Uem9xU1NCNUUwYmduV0kxeW5fMjBZQ1REbkRsVTZ0UDMtY3FFU3BBTEsyMTlRdkxGZWJ3MmlmVDRuTExuVGR2QQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/newsletter.xlsx
+++ b/docs/newsletter.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG Deal Intelligence" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FMCG Deal Intelligence'!$A$1:$N$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +49,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001A478A"/>
         <bgColor rgb="001A478A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-        <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,14 +84,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -557,17 +550,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snacks maker Utz Brands to be taken private in $2.9 billion deal - CNBC</t>
+          <t>Charoen Pokphand Foods Reports Acquisition Of Unit Engaged In Beverage Business In Vietnam - TradingView</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CNBC</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -575,149 +568,41 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>$2.9 billion</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Charoen Pokphand Foods</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Utz Brands</t>
+          <t>unit engaged in beverage business in Vietnam</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>92.2</v>
+        <v>73</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Tier 2 — Reputable</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOXzlna2ppTjc0RHJDOUstcWlSSHd4Vm9HS0hjVWZXemtmMGJhUmdUbXhUZFRCWWRnSzZQblRCV0NhZTdDb2R0QmphV19pc0t1cjBWQmpFbGRRYjkxYW41cXhVRGd0QWVmQmtaNGt5NUQ4ZjBjS2xNcGdMUVo0Z09pSnQ2NTNGTC1xM1NJYW5PWjlIaEM3UGdSU1JNSGRJc0FxcDFyTEhxUdIBrAFBVV95cUxQS09fWkZQeUoycDktN1pmUThQeHpKM2cydnJvdXpUUnc2cW5yY2JMWmE2Z0gyMzJsYUpMTDhDZUpnVXlacW45dTlFZWt1M3ZhNWpkWmFZYWdkeE1jclR4dkhnVnowbUtPVVFnMDFHa3YzOWNYLTVkMmdFSHdRdFUySGxUQ25OeFMxRGwtRnluQ0dIZjBZWE8waFhGSm5JdXFNME1ELUluOW5QRkdI?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Wipro Consumer Care Strengthens FMCG Leading Position in APAC Market with the Acquisition of S Brands - macaubusiness.com</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>macaubusiness.com</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Wipro Consumer Care</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>S Brands</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNazE5WUxXbVlIWENqdWFtSWZDQVQtRnRTalFjU2ZVVTlpRTRwWko1cmFLYjFFNTREQVRic1JWZEVndWhyWTlZVE92bFdrZjJiNkdENVpWdjk4LUl5b2Naa3dtUVRVZHBQbHUxWTg0dERpQTlCbnYzY2lKR19OZC1aS2VGdU1XVUMxNW5BdWRSNkFXaE5rZUlQeTBtOGx1c1lyN0ZRdzhZR0JVRnhhSFViUXZ2dkpZV2luMU9OVkJtbGNYRVdDN2dF?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Truelink Capital Completes Acquisition of Lyons Magnus, a Leading Developer and Manufacturer of Specialty Ingredients, Beverage, and Nutrition Solutions - PR Newswire</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>PR Newswire</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Truelink Capital</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Lyons Magnus</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxOeFRtam5ubkFVczVYcmtvN0RPRFUweHYwM3RhX05tLUE1RWQ5SXdTSElMU1dkcl9UV0R4QnQ5YjB3aWxiM19mbGNXN2pQLXlKYTg2emlfbG0yYkhRaC1CV1B4OUVnd3NkR2t5V1FPVGtpN0FiTDc3TW9CeWZxakhrcEEtMTh2TFVseTdNb3R1UnM3MlpVY1Zzb19pTjRoTHFZU3RoQkRVTEdBXzc4Z01tN2ItamVrQnpSdUdLTW5udDc1TV9iQlFadjZjZlY0eWtIR211ZEQ1NElJbXpvck9GZW1LblE4MndUeno5RC1Uem9xU1NCNUUwYmduV0kxeW5fMjBZQ1REbkRsVTZ0UDMtY3FFU3BBTEsyMTlRdkxGZWJ3MmlmVDRuTExuVGR2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPVGNoMlcydW50T05POUhRa19JMDd1eXVaTmE4ajV0WFlGMlM5NTNOY3F3TXJuV2tJbVhHZ1hiVVI5a3ZBOFNkeUdtam43R0l5THRFay0zbW9NWmtQSjJHQTFyN0ZMYmN1RWNORnc5d3VoM1JlV044MlB1YmN2NHF2SG5fUHlqMnZKVzVFTUQtcjlHTVVkOVNqVkNLT1JiR3BrV0ZmWkhNcEpaWmlIYjZXd1kzNGlCbE5OV2M1ZVllckY3aDBqNmQ5Q0pwMVpWNExjd1N4Uy1IMGlHLWhOLUpaUjVyV2NPMjgwMERmQW93S2VuQQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>